--- a/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T09:05:38+00:00</t>
+    <t>2024-04-08T11:51:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T11:51:49+00:00</t>
+    <t>2024-04-08T12:00:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:00:05+00:00</t>
+    <t>2024-04-08T12:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:44:30+00:00</t>
+    <t>2024-04-08T12:53:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:16+00:00</t>
+    <t>2024-04-08T13:02:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/MP-QA/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:02:05+00:00</t>
+    <t>2024-04-08T13:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
